--- a/data/safety_toolbox.xlsx
+++ b/data/safety_toolbox.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -31,10 +31,35 @@
     <t>Participants</t>
   </si>
   <si>
+    <t>Notes/ Discussion Summary</t>
+  </si>
+  <si>
+    <t>Created_At</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>Created_At</t>
+    <t>617d418b783f44708fcf6ffd4ec2290e</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>Accident Reporting</t>
+  </si>
+  <si>
+    <t>George Shonga</t>
+  </si>
+  <si>
+    <t>Herbicide team</t>
+  </si>
+  <si>
+    <t>2025-12-02T19:16:08.573926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reporting accidents at work place_x000D_
+                </t>
   </si>
 </sst>
 </file>
@@ -392,10 +417,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -416,6 +441,32 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
